--- a/dataset/Outlet.xlsx
+++ b/dataset/Outlet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malinijayaweera/Desktop/Optimization Assignment/OM-Assignment/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84E4CA1D-933E-3D45-9A61-FD70C4189D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7AD56B-2C3D-9C40-9982-B0B0901F93FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{96654654-F19B-6444-A4F6-CEBB723895CA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" xr2:uid="{96654654-F19B-6444-A4F6-CEBB723895CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Outlet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
   <si>
     <t>Amman Stores</t>
   </si>
@@ -46,51 +46,18 @@
     <t>FARSHANA HOTEL</t>
   </si>
   <si>
-    <t>GRAIN STORES</t>
-  </si>
-  <si>
-    <t>Ishara snackers .</t>
-  </si>
-  <si>
-    <t>ISURU STORES</t>
-  </si>
-  <si>
-    <t>Jayaneris bakery</t>
-  </si>
-  <si>
-    <t>K S PERERA</t>
-  </si>
-  <si>
-    <t>Kavinda bake house</t>
-  </si>
-  <si>
-    <t>Lakmal Stores</t>
-  </si>
-  <si>
-    <t>Metro Pex Traders</t>
-  </si>
-  <si>
     <t>Nadan stores</t>
   </si>
   <si>
     <t>PRAGATHI STORES</t>
   </si>
   <si>
-    <t>Rashini stores</t>
-  </si>
-  <si>
     <t>ROYAL FOOD CENTER</t>
   </si>
   <si>
     <t>SANJANA GRAM</t>
   </si>
   <si>
-    <t>SRI KALASALA</t>
-  </si>
-  <si>
-    <t>Telebrow Canteen</t>
-  </si>
-  <si>
     <t>UPUL HOTEL</t>
   </si>
   <si>
@@ -103,9 +70,6 @@
     <t>MANIKEGE KADE</t>
   </si>
   <si>
-    <t>THARINDI STORES</t>
-  </si>
-  <si>
     <t>HEMALI STORES</t>
   </si>
   <si>
@@ -118,9 +82,6 @@
     <t>KUMARA STORES</t>
   </si>
   <si>
-    <t>DILINI STORES</t>
-  </si>
-  <si>
     <t>IDUWARA STORES</t>
   </si>
   <si>
@@ -139,15 +100,9 @@
     <t>MADUWANTHI TRADERS</t>
   </si>
   <si>
-    <t>UDESHIKA STORES</t>
-  </si>
-  <si>
     <t>HEMARATHNA STORES</t>
   </si>
   <si>
-    <t>CHANDIMA STORES</t>
-  </si>
-  <si>
     <t>SHANTHA STORES</t>
   </si>
   <si>
@@ -166,18 +121,9 @@
     <t>PERERA SHOP</t>
   </si>
   <si>
-    <t>WISDOM PHARMACY &amp; GROCERY</t>
-  </si>
-  <si>
-    <t>R.N STORES</t>
-  </si>
-  <si>
     <t>GAMAGE STORES</t>
   </si>
   <si>
-    <t>D R N STORES</t>
-  </si>
-  <si>
     <t>Chamila Stores</t>
   </si>
   <si>
@@ -211,60 +157,21 @@
     <t>SUBASINGHE STORES</t>
   </si>
   <si>
-    <t>PRASADI STORES</t>
-  </si>
-  <si>
-    <t>Jayasinghe Vege Shop</t>
-  </si>
-  <si>
     <t>A D FRUITS</t>
   </si>
   <si>
-    <t>SILVA STORES</t>
-  </si>
-  <si>
-    <t>SILVERLINE GROCERY</t>
-  </si>
-  <si>
-    <t>PRASHADI STORES</t>
-  </si>
-  <si>
-    <t>RUHUNU TRADERS</t>
-  </si>
-  <si>
-    <t>YUKEE PHARMACY</t>
-  </si>
-  <si>
     <t>DAILY FOODS</t>
   </si>
   <si>
-    <t>HANSANA STORES</t>
-  </si>
-  <si>
-    <t>PUBUDU STORES</t>
-  </si>
-  <si>
-    <t>Everfresh Bakers</t>
-  </si>
-  <si>
     <t>RAJAPAKSHA STORES</t>
   </si>
   <si>
     <t>MALLIKA STORES</t>
   </si>
   <si>
-    <t>UPUL VEGETABLE</t>
-  </si>
-  <si>
     <t>RUHUNU MILK BAR</t>
   </si>
   <si>
-    <t>Dhanushka Grocery Mart</t>
-  </si>
-  <si>
-    <t>Wasudewa Stores</t>
-  </si>
-  <si>
     <t>THUSHARI TRADE CENTRE</t>
   </si>
   <si>
@@ -289,39 +196,12 @@
     <t>109,Avissawella road, Orugodawatta</t>
   </si>
   <si>
-    <t>118,Avissawella road,Orugodawatta</t>
-  </si>
-  <si>
-    <t>231,Kandy road, Peliyagoda</t>
-  </si>
-  <si>
-    <t>36/c,Avissawella road,Orugodawatta</t>
-  </si>
-  <si>
-    <t>635,Wilahena road,Gonawala</t>
-  </si>
-  <si>
-    <t>633,Wilahena road, Gonawala</t>
-  </si>
-  <si>
-    <t>89,Station road,Kelaniya</t>
-  </si>
-  <si>
-    <t>107,parakrama road,Peliyagoda</t>
-  </si>
-  <si>
-    <t>191/27,Avissawella road,Orugodawatta</t>
-  </si>
-  <si>
     <t>85/137,Avissawella road, Orugodawatta</t>
   </si>
   <si>
     <t>15,Avissawella road, Orugodawatta</t>
   </si>
   <si>
-    <t>179/110a,Avissawella road,Orugodawatta</t>
-  </si>
-  <si>
     <t>56,Avissawella road,Orugodawatta</t>
   </si>
   <si>
@@ -331,9 +211,6 @@
     <t>287,Kandy road,Peliyagoda</t>
   </si>
   <si>
-    <t>38/a,Bandaranayake road, Kelaniya</t>
-  </si>
-  <si>
     <t>123, Biyagama road, Pattiya</t>
   </si>
   <si>
@@ -346,9 +223,6 @@
     <t>469/22,Kandy road, Kelaniya</t>
   </si>
   <si>
-    <t>469/18,Kandy road, Kelaniya</t>
-  </si>
-  <si>
     <t>Latitude</t>
   </si>
   <si>
@@ -367,15 +241,9 @@
     <t>63,,Dutugamunu mawatha</t>
   </si>
   <si>
-    <t>86/59a,Dutugamunu mawatha</t>
-  </si>
-  <si>
     <t>360/3,Dutugamunu mawatha</t>
   </si>
   <si>
-    <t>20/20/1,Dutugamunu mawatha</t>
-  </si>
-  <si>
     <t>94/2,Dutugamunu mawatha</t>
   </si>
   <si>
@@ -385,24 +253,12 @@
     <t>608,first floor</t>
   </si>
   <si>
-    <t>485,petiyagoda,kelaniya</t>
-  </si>
-  <si>
     <t>70/a,biyagama road</t>
   </si>
   <si>
-    <t>437/a,gonagampala,pilapiyiya,kelaniya</t>
-  </si>
-  <si>
     <t>282/a,kandy road,peliyagoda</t>
   </si>
   <si>
-    <t>418/b,biyagama road</t>
-  </si>
-  <si>
-    <t>342, biyagama road</t>
-  </si>
-  <si>
     <t>115/b,biyagama road</t>
   </si>
   <si>
@@ -427,9 +283,6 @@
     <t>152,dippitiya road, Dalugama</t>
   </si>
   <si>
-    <t>156,dippitiya road, Dalugama</t>
-  </si>
-  <si>
     <t>565, eriyawatiya</t>
   </si>
   <si>
@@ -466,45 +319,12 @@
     <t>457/a, kandy road</t>
   </si>
   <si>
-    <t>111, wewalduwa</t>
-  </si>
-  <si>
-    <t>141/a, dalugama</t>
-  </si>
-  <si>
-    <t>550, thorana junction</t>
-  </si>
-  <si>
     <t>732/a, thorana junctiion</t>
   </si>
   <si>
-    <t>45,dippitigoda road</t>
-  </si>
-  <si>
-    <t>120/4,Station Road,Thorana Junction,Kelaniya</t>
-  </si>
-  <si>
-    <t>33/1,Dipitigoda Road,Pattiya</t>
-  </si>
-  <si>
-    <t>91,Biyagama Road,Tyre Junction</t>
-  </si>
-  <si>
-    <t>5/2,Dipitigoda Road,Near Thorana Junction</t>
-  </si>
-  <si>
     <t>210,Kandy Road,Tyre Junction,Peliyagoda</t>
   </si>
   <si>
-    <t>18/A,Dipitigoda Road,Gonawala</t>
-  </si>
-  <si>
-    <t>74/6,Temple Lane,Thorana Junction</t>
-  </si>
-  <si>
-    <t>150,Biyagama Road,Pattiya</t>
-  </si>
-  <si>
     <t>12/A,Dipitigoda Road,Thorana Junction,Kelaniya</t>
   </si>
   <si>
@@ -514,22 +334,10 @@
     <t>78,Baseline Road,Near Tyre Junction,Kelaniya</t>
   </si>
   <si>
-    <t>102/3,Dipitigoda Road,Gonawala</t>
-  </si>
-  <si>
     <t>56/7,Old Kandy Road,Tyre Junction,Peliyagoda</t>
   </si>
   <si>
-    <t>23,Biyagama Road,Thorana Junction</t>
-  </si>
-  <si>
-    <t>89/2,Dipitigoda Road,Kelaniya</t>
-  </si>
-  <si>
     <t>14/5,Temple Road,Near Tyre Junction</t>
-  </si>
-  <si>
-    <t>67,Dipitigoda Road,Gonawala Junction</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A173C5FC-AD52-1D43-95CE-7528396D004E}">
-  <dimension ref="A1:Y90"/>
+  <dimension ref="A1:Y56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -1416,10 +1224,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="E1" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1430,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>6.9429999999999996</v>
@@ -1447,7 +1255,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>6.9231490000000004</v>
@@ -1464,7 +1272,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>6.9431000000000003</v>
@@ -1481,7 +1289,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>6.9593999999999996</v>
@@ -1498,7 +1306,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>6.9432999999999998</v>
@@ -1509,1406 +1317,813 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>19219</v>
+        <v>1035964</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>6.9433999999999996</v>
+        <v>6.9444999999999997</v>
       </c>
       <c r="E7">
-        <v>79.8827</v>
+        <v>79.884</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1049191</v>
+        <v>19241</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>6.9553000000000003</v>
+        <v>6.9424999999999999</v>
       </c>
       <c r="E8">
-        <v>79.878699999999995</v>
+        <v>79.882000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>289781</v>
+        <v>236970</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
-        <v>91</v>
+      <c r="C9" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="D9">
-        <v>6.9429999999999996</v>
+        <v>6.9432999999999998</v>
       </c>
       <c r="E9">
-        <v>79.882199999999997</v>
+        <v>79.882900000000006</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1059497</v>
+        <v>235822</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
-        <v>92</v>
+      <c r="C10" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>6.9625000000000004</v>
+        <v>6.944</v>
       </c>
       <c r="E10">
-        <v>79.928100000000001</v>
+        <v>79.883499999999998</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>681720</v>
+        <v>19213</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="D11">
-        <v>6.9623999999999997</v>
+        <v>6.9584999999999999</v>
       </c>
       <c r="E11">
-        <v>79.927999999999997</v>
+        <v>79.926500000000004</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1052985</v>
+        <v>173578</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>6.9568000000000003</v>
+        <v>6.9436999999999998</v>
       </c>
       <c r="E12">
-        <v>79.914500000000004</v>
+        <v>79.883200000000002</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1050100</v>
+      <c r="A13" s="1">
+        <v>19526</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>6.9539999999999997</v>
+        <v>6.9604999999999997</v>
       </c>
       <c r="E13">
-        <v>79.879499999999993</v>
+        <v>79.881</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1025958</v>
+      <c r="A14" s="1">
+        <v>682270</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14">
-        <v>6.9432</v>
-      </c>
-      <c r="E14">
-        <v>79.882499999999993</v>
+        <v>66</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6.9678000000000004</v>
+      </c>
+      <c r="E14" s="1">
+        <v>79.881600000000006</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1035964</v>
+      <c r="A15" s="1">
+        <v>19510</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="D15">
-        <v>6.9444999999999997</v>
+        <v>6.9618000000000002</v>
       </c>
       <c r="E15">
-        <v>79.884</v>
+        <v>79.881200000000007</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>19241</v>
+      <c r="A16" s="1">
+        <v>19525</v>
       </c>
       <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16">
+        <v>6.9626000000000001</v>
+      </c>
+      <c r="E16">
+        <v>79.881299999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>156783</v>
+      </c>
+      <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16">
-        <v>6.9424999999999999</v>
-      </c>
-      <c r="E16">
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17">
+        <v>6.9634</v>
+      </c>
+      <c r="E17">
+        <v>79.881399999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>19522</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18">
+        <v>6.9641999999999999</v>
+      </c>
+      <c r="E18">
+        <v>79.881500000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>263554</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19">
+        <v>6.9657999999999998</v>
+      </c>
+      <c r="E19">
+        <v>79.881699999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>187254</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20">
+        <v>6.9672000000000001</v>
+      </c>
+      <c r="E20">
+        <v>79.881900000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>191574</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21">
+        <v>6.968</v>
+      </c>
+      <c r="E21">
         <v>79.882000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>1038859</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17">
-        <v>6.9450000000000003</v>
-      </c>
-      <c r="E17">
-        <v>79.884500000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>236970</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18">
-        <v>6.9432999999999998</v>
-      </c>
-      <c r="E18">
-        <v>79.882900000000006</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>235822</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19">
-        <v>6.944</v>
-      </c>
-      <c r="E19">
-        <v>79.883499999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>267031</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20">
-        <v>6.9554999999999998</v>
-      </c>
-      <c r="E20">
-        <v>79.915800000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>1035965</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>334942</v>
+      </c>
+      <c r="B22" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21">
-        <v>6.9561999999999999</v>
-      </c>
-      <c r="E21">
-        <v>79.879300000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>19213</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D22">
-        <v>6.9584999999999999</v>
+        <v>6.9699</v>
       </c>
       <c r="E22">
-        <v>79.926500000000004</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>173578</v>
+      <c r="A23" s="1">
+        <v>312806</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="D23">
-        <v>6.9436999999999998</v>
+        <v>6.9489000000000001</v>
       </c>
       <c r="E23">
-        <v>79.883200000000002</v>
+        <v>79.901200000000003</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>19526</v>
+        <v>19296</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D24">
-        <v>6.9604999999999997</v>
+        <v>6.9478</v>
       </c>
       <c r="E24">
-        <v>79.881</v>
+        <v>79.912499999999994</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>682270</v>
+        <v>179686</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="1">
-        <v>6.9678000000000004</v>
-      </c>
-      <c r="E25" s="1">
-        <v>79.881600000000006</v>
+        <v>77</v>
+      </c>
+      <c r="D25">
+        <v>6.9469000000000003</v>
+      </c>
+      <c r="E25">
+        <v>79.918000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>682593</v>
+        <v>19289</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="1">
-        <v>6.9675000000000002</v>
-      </c>
-      <c r="E26" s="1">
-        <v>79.881500000000003</v>
+        <v>78</v>
+      </c>
+      <c r="D26">
+        <v>6.9485000000000001</v>
+      </c>
+      <c r="E26">
+        <v>79.902000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>19510</v>
+        <v>19290</v>
       </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D27">
-        <v>6.9618000000000002</v>
+        <v>6.9462000000000002</v>
       </c>
       <c r="E27">
-        <v>79.881200000000007</v>
+        <v>79.920500000000004</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>19525</v>
+        <v>19292</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D28">
-        <v>6.9626000000000001</v>
+        <v>6.9455999999999998</v>
       </c>
       <c r="E28">
-        <v>79.881299999999996</v>
+        <v>79.925799999999995</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>156783</v>
+        <v>19474</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="D29">
-        <v>6.9634</v>
+        <v>6.9471999999999996</v>
       </c>
       <c r="E29">
-        <v>79.881399999999999</v>
+        <v>79.915000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>19522</v>
+        <v>342007</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="D30">
-        <v>6.9641999999999999</v>
+        <v>6.9486999999999997</v>
       </c>
       <c r="E30">
-        <v>79.881500000000003</v>
+        <v>79.907200000000003</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>669010</v>
+        <v>1050231</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="D31">
-        <v>6.9649999999999999</v>
+        <v>6.9467999999999996</v>
       </c>
       <c r="E31">
-        <v>79.881600000000006</v>
+        <v>79.917199999999994</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>263554</v>
+        <v>19488</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="D32">
-        <v>6.9657999999999998</v>
+        <v>6.9695999999999998</v>
       </c>
       <c r="E32">
-        <v>79.881699999999995</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.913399999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>243284</v>
+        <v>1025942</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="D33">
-        <v>6.9665999999999997</v>
+        <v>6.9688999999999997</v>
       </c>
       <c r="E33">
-        <v>79.881799999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.912300000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>187254</v>
+        <v>1025946</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D34">
-        <v>6.9672000000000001</v>
+        <v>6.9684999999999997</v>
       </c>
       <c r="E34">
-        <v>79.881900000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.911799999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>191574</v>
+        <v>341989</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="D35">
+        <v>6.9682000000000004</v>
+      </c>
+      <c r="E35">
+        <v>79.911199999999994</v>
+      </c>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>197247</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36">
         <v>6.968</v>
       </c>
-      <c r="E35">
-        <v>79.882000000000005</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
-        <v>334942</v>
-      </c>
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36">
-        <v>6.9699</v>
-      </c>
       <c r="E36">
-        <v>79.89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.910899999999998</v>
+      </c>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>312806</v>
+        <v>266594</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D37">
-        <v>6.9489000000000001</v>
+        <v>6.9683000000000002</v>
       </c>
       <c r="E37">
-        <v>79.901200000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.910600000000002</v>
+      </c>
+      <c r="W37" s="1"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>19296</v>
+        <v>1025956</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="D38">
-        <v>6.9478</v>
+        <v>6.9687000000000001</v>
       </c>
       <c r="E38">
-        <v>79.912499999999994</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.910499999999999</v>
+      </c>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>19309</v>
+        <v>270094</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D39">
-        <v>6.9481999999999999</v>
+        <v>6.9691000000000001</v>
       </c>
       <c r="E39">
-        <v>79.905799999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.910700000000006</v>
+      </c>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>179686</v>
+        <v>127840</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D40">
-        <v>6.9469000000000003</v>
+        <v>6.9695</v>
       </c>
       <c r="E40">
-        <v>79.918000000000006</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.911000000000001</v>
+      </c>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>19249</v>
+        <v>1025945</v>
       </c>
       <c r="B41" t="s">
         <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="D41">
-        <v>6.9492000000000003</v>
+        <v>6.9698000000000002</v>
       </c>
       <c r="E41">
-        <v>79.909499999999994</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79.9114</v>
+      </c>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>19289</v>
+        <v>25200</v>
       </c>
       <c r="B42" t="s">
         <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D42">
-        <v>6.9485000000000001</v>
+        <v>6.97</v>
       </c>
       <c r="E42">
-        <v>79.902000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <v>19290</v>
+        <v>79.911900000000003</v>
+      </c>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>264612</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="D43">
-        <v>6.9462000000000002</v>
+        <v>6.9702000000000002</v>
       </c>
       <c r="E43">
-        <v>79.920500000000004</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <v>19292</v>
+        <v>79.912400000000005</v>
+      </c>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>19344</v>
       </c>
       <c r="B44" t="s">
         <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D44">
-        <v>6.9455999999999998</v>
+        <v>6.9701000000000004</v>
       </c>
       <c r="E44">
-        <v>79.925799999999995</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
-        <v>19474</v>
+        <v>79.912899999999993</v>
+      </c>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>679300</v>
       </c>
       <c r="B45" t="s">
         <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="D45">
-        <v>6.9471999999999996</v>
+        <v>6.9686000000000003</v>
       </c>
       <c r="E45">
-        <v>79.915000000000006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="1">
-        <v>342007</v>
+        <v>79.913600000000002</v>
+      </c>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="1:23" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>19345</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
       </c>
-      <c r="C46" t="s">
-        <v>128</v>
+      <c r="C46" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D46">
-        <v>6.9486999999999997</v>
+        <v>6.9682000000000004</v>
       </c>
       <c r="E46">
-        <v>79.907200000000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="1">
-        <v>1050231</v>
+        <v>79.910799999999995</v>
+      </c>
+      <c r="W46" s="1"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>19349</v>
       </c>
       <c r="B47" t="s">
         <v>47</v>
       </c>
-      <c r="C47" t="s">
-        <v>127</v>
+      <c r="C47" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D47">
-        <v>6.9467999999999996</v>
+        <v>6.9698000000000002</v>
       </c>
       <c r="E47">
-        <v>79.917199999999994</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="1">
-        <v>681940</v>
+        <v>79.910799999999995</v>
+      </c>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>19354</v>
       </c>
       <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48">
+        <v>6.9701000000000004</v>
+      </c>
+      <c r="E48">
+        <v>79.911100000000005</v>
+      </c>
+      <c r="W48" s="1"/>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>22672</v>
+      </c>
+      <c r="B49" t="s">
         <v>48</v>
       </c>
-      <c r="C48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48">
-        <v>6.9474999999999998</v>
-      </c>
-      <c r="E48">
-        <v>79.913499999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A49" s="1">
-        <v>309088</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="C49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49">
+        <v>6.9702999999999999</v>
+      </c>
+      <c r="E49">
+        <v>79.911600000000007</v>
+      </c>
+      <c r="W49" s="1"/>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>19334</v>
+      </c>
+      <c r="B50" t="s">
         <v>49</v>
       </c>
-      <c r="C49" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49">
-        <v>6.9465000000000003</v>
-      </c>
-      <c r="E49">
-        <v>79.918999999999997</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
-        <v>19488</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="C50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50">
+        <v>6.9702999999999999</v>
+      </c>
+      <c r="E50">
+        <v>79.912599999999998</v>
+      </c>
+      <c r="W50" s="1"/>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>19356</v>
+      </c>
+      <c r="B51" t="s">
         <v>50</v>
       </c>
-      <c r="C50" t="s">
-        <v>134</v>
-      </c>
-      <c r="D50">
-        <v>6.9695999999999998</v>
-      </c>
-      <c r="E50">
-        <v>79.913399999999996</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A51" s="1">
-        <v>1080604</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="C51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51">
+        <v>6.9692999999999996</v>
+      </c>
+      <c r="E51">
+        <v>79.913799999999995</v>
+      </c>
+      <c r="W51" s="1"/>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>1080606</v>
+      </c>
+      <c r="B52" t="s">
         <v>51</v>
       </c>
-      <c r="C51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D51">
-        <v>6.9691999999999998</v>
-      </c>
-      <c r="E51">
-        <v>79.912899999999993</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A52" s="1">
-        <v>1025942</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>52</v>
       </c>
-      <c r="C52" t="s">
-        <v>136</v>
-      </c>
       <c r="D52">
-        <v>6.9688999999999997</v>
+        <v>6.9704533333333298</v>
       </c>
       <c r="E52">
-        <v>79.912300000000002</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A53" s="1">
-        <v>1025946</v>
-      </c>
-      <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53">
-        <v>6.9684999999999997</v>
-      </c>
-      <c r="E53">
-        <v>79.911799999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A54" s="1">
-        <v>341989</v>
-      </c>
-      <c r="B54" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" t="s">
-        <v>138</v>
-      </c>
-      <c r="D54">
-        <v>6.9682000000000004</v>
-      </c>
-      <c r="E54">
-        <v>79.911199999999994</v>
-      </c>
+        <v>79.9119843859649</v>
+      </c>
+      <c r="W52" s="1"/>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W53" s="1"/>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W54" s="1"/>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A55" s="1">
-        <v>197247</v>
-      </c>
-      <c r="B55" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" t="s">
-        <v>139</v>
-      </c>
-      <c r="D55">
-        <v>6.968</v>
-      </c>
-      <c r="E55">
-        <v>79.910899999999998</v>
-      </c>
-      <c r="W55" s="1"/>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A56" s="1">
-        <v>266594</v>
-      </c>
-      <c r="B56" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" t="s">
-        <v>140</v>
-      </c>
-      <c r="D56">
-        <v>6.9683000000000002</v>
-      </c>
-      <c r="E56">
-        <v>79.910600000000002</v>
-      </c>
-      <c r="W56" s="1"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A57" s="1">
-        <v>1025956</v>
-      </c>
-      <c r="B57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" t="s">
-        <v>141</v>
-      </c>
-      <c r="D57">
-        <v>6.9687000000000001</v>
-      </c>
-      <c r="E57">
-        <v>79.910499999999999</v>
-      </c>
-      <c r="W57" s="1"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A58" s="1">
-        <v>270094</v>
-      </c>
-      <c r="B58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58">
-        <v>6.9691000000000001</v>
-      </c>
-      <c r="E58">
-        <v>79.910700000000006</v>
-      </c>
-      <c r="W58" s="1"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A59" s="1">
-        <v>127840</v>
-      </c>
-      <c r="B59" t="s">
-        <v>30</v>
-      </c>
-      <c r="C59" t="s">
-        <v>143</v>
-      </c>
-      <c r="D59">
-        <v>6.9695</v>
-      </c>
-      <c r="E59">
-        <v>79.911000000000001</v>
-      </c>
-      <c r="W59" s="1"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A60" s="1">
-        <v>1025945</v>
-      </c>
-      <c r="B60" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60" t="s">
-        <v>144</v>
-      </c>
-      <c r="D60">
-        <v>6.9698000000000002</v>
-      </c>
-      <c r="E60">
-        <v>79.9114</v>
-      </c>
-      <c r="W60" s="1"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A61" s="1">
-        <v>25200</v>
-      </c>
-      <c r="B61" t="s">
-        <v>60</v>
-      </c>
-      <c r="C61" t="s">
-        <v>145</v>
-      </c>
-      <c r="D61">
-        <v>6.97</v>
-      </c>
-      <c r="E61">
-        <v>79.911900000000003</v>
-      </c>
-      <c r="W61" s="1"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>264612</v>
-      </c>
-      <c r="B62" t="s">
-        <v>61</v>
-      </c>
-      <c r="C62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D62">
-        <v>6.9702000000000002</v>
-      </c>
-      <c r="E62">
-        <v>79.912400000000005</v>
-      </c>
-      <c r="W62" s="1"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>19344</v>
-      </c>
-      <c r="B63" t="s">
-        <v>62</v>
-      </c>
-      <c r="C63" t="s">
-        <v>147</v>
-      </c>
-      <c r="D63">
-        <v>6.9701000000000004</v>
-      </c>
-      <c r="E63">
-        <v>79.912899999999993</v>
-      </c>
-      <c r="W63" s="1"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>19332</v>
-      </c>
-      <c r="B64" t="s">
-        <v>63</v>
-      </c>
-      <c r="C64" t="s">
-        <v>148</v>
-      </c>
-      <c r="D64">
-        <v>6.9699</v>
-      </c>
-      <c r="E64">
-        <v>79.913300000000007</v>
-      </c>
-      <c r="W64" s="1"/>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>19337</v>
-      </c>
-      <c r="B65" t="s">
-        <v>50</v>
-      </c>
-      <c r="C65" t="s">
-        <v>149</v>
-      </c>
-      <c r="D65">
-        <v>6.9694000000000003</v>
-      </c>
-      <c r="E65">
-        <v>79.913700000000006</v>
-      </c>
-      <c r="W65" s="1"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>1047838</v>
-      </c>
-      <c r="B66" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" t="s">
-        <v>150</v>
-      </c>
-      <c r="D66">
-        <v>6.9690000000000003</v>
-      </c>
-      <c r="E66">
-        <v>79.913899999999998</v>
-      </c>
-      <c r="W66" s="1"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>679300</v>
-      </c>
-      <c r="B67" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" t="s">
-        <v>151</v>
-      </c>
-      <c r="D67">
-        <v>6.9686000000000003</v>
-      </c>
-      <c r="E67">
-        <v>79.913600000000002</v>
-      </c>
-      <c r="W67" s="1"/>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>342568</v>
-      </c>
-      <c r="B68" t="s">
-        <v>66</v>
-      </c>
-      <c r="C68" t="s">
-        <v>152</v>
-      </c>
-      <c r="D68">
-        <v>6.9683000000000002</v>
-      </c>
-      <c r="E68">
-        <v>79.913200000000003</v>
-      </c>
-      <c r="W68" s="1"/>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>19352</v>
-      </c>
-      <c r="B69" t="s">
-        <v>67</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D69">
-        <v>6.9680999999999997</v>
-      </c>
-      <c r="E69">
-        <v>79.912700000000001</v>
-      </c>
-      <c r="W69" s="1"/>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>19343</v>
-      </c>
-      <c r="B70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D70">
-        <v>6.9679000000000002</v>
-      </c>
-      <c r="E70">
-        <v>79.912199999999999</v>
-      </c>
-      <c r="W70" s="1"/>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>19357</v>
-      </c>
-      <c r="B71" t="s">
-        <v>69</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D71">
-        <v>6.9678000000000004</v>
-      </c>
-      <c r="E71">
-        <v>79.911699999999996</v>
-      </c>
-      <c r="W71" s="1"/>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>130898</v>
-      </c>
-      <c r="B72" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D72">
-        <v>6.9679000000000002</v>
-      </c>
-      <c r="E72">
-        <v>79.911199999999994</v>
-      </c>
-      <c r="W72" s="1"/>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>19345</v>
-      </c>
-      <c r="B73" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D73">
-        <v>6.9682000000000004</v>
-      </c>
-      <c r="E73">
-        <v>79.910799999999995</v>
-      </c>
-      <c r="W73" s="1"/>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>238361</v>
-      </c>
-      <c r="B74" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D74">
-        <v>6.9686000000000003</v>
-      </c>
-      <c r="E74">
-        <v>79.910600000000002</v>
-      </c>
-      <c r="W74" s="1"/>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>277000</v>
-      </c>
-      <c r="B75" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D75">
-        <v>6.9690000000000003</v>
-      </c>
-      <c r="E75">
-        <v>79.910499999999999</v>
-      </c>
-      <c r="W75" s="1"/>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>1047839</v>
-      </c>
-      <c r="B76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D76">
-        <v>6.9694000000000003</v>
-      </c>
-      <c r="E76">
-        <v>79.910600000000002</v>
-      </c>
-      <c r="W76" s="1"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>19349</v>
-      </c>
-      <c r="B77" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D77">
-        <v>6.9698000000000002</v>
-      </c>
-      <c r="E77">
-        <v>79.910799999999995</v>
-      </c>
-      <c r="W77" s="1"/>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>19354</v>
-      </c>
-      <c r="B78" t="s">
-        <v>61</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D78">
-        <v>6.9701000000000004</v>
-      </c>
-      <c r="E78">
-        <v>79.911100000000005</v>
-      </c>
-      <c r="W78" s="1"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>22672</v>
-      </c>
-      <c r="B79" t="s">
-        <v>76</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D79">
-        <v>6.9702999999999999</v>
-      </c>
-      <c r="E79">
-        <v>79.911600000000007</v>
-      </c>
-      <c r="W79" s="1"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>679281</v>
-      </c>
-      <c r="B80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D80">
-        <v>6.9703999999999997</v>
-      </c>
-      <c r="E80">
-        <v>79.912099999999995</v>
-      </c>
-      <c r="W80" s="1"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>19334</v>
-      </c>
-      <c r="B81" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D81">
-        <v>6.9702999999999999</v>
-      </c>
-      <c r="E81">
-        <v>79.912599999999998</v>
-      </c>
-      <c r="W81" s="1"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>1052077</v>
-      </c>
-      <c r="B82" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D82">
-        <v>6.9701000000000004</v>
-      </c>
-      <c r="E82">
-        <v>79.912999999999997</v>
-      </c>
-      <c r="W82" s="1"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>1025957</v>
-      </c>
-      <c r="B83" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D83">
-        <v>6.9696999999999996</v>
-      </c>
-      <c r="E83">
-        <v>79.913499999999999</v>
-      </c>
-      <c r="W83" s="1"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A84">
-        <v>19356</v>
-      </c>
-      <c r="B84" t="s">
-        <v>81</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D84">
-        <v>6.9692999999999996</v>
-      </c>
-      <c r="E84">
-        <v>79.913799999999995</v>
-      </c>
-      <c r="W84" s="1"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>271876</v>
-      </c>
-      <c r="B85" t="s">
-        <v>42</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D85">
-        <v>6.9703298245614</v>
-      </c>
-      <c r="E85">
-        <v>79.911992982456198</v>
-      </c>
-      <c r="W85" s="1"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>1080606</v>
-      </c>
-      <c r="B86" t="s">
-        <v>82</v>
-      </c>
-      <c r="C86" t="s">
-        <v>83</v>
-      </c>
-      <c r="D86">
-        <v>6.9704533333333298</v>
-      </c>
-      <c r="E86">
-        <v>79.9119843859649</v>
-      </c>
-      <c r="W86" s="1"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="W87" s="1"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="W88" s="1"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Y90" t="s">
-        <v>133</v>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y56" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/Outlet.xlsx
+++ b/dataset/Outlet.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malinijayaweera/Desktop/Optimization Assignment/OM-Assignment/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7AD56B-2C3D-9C40-9982-B0B0901F93FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27046201-8DA2-6C4D-9BE0-A6A91AD13C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" xr2:uid="{96654654-F19B-6444-A4F6-CEBB723895CA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{96654654-F19B-6444-A4F6-CEBB723895CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Outlet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2081,7 +2094,7 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>19356</v>
+        <v>19334</v>
       </c>
       <c r="B51" t="s">
         <v>50</v>
